--- a/deliverables/flexy-fra-financial-model/Flexy_FRA_Financial_Model_Year1_Year5_FINAL.xlsx
+++ b/deliverables/flexy-fra-financial-model/Flexy_FRA_Financial_Model_Year1_Year5_FINAL.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="1526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="1527">
   <si>
     <t xml:space="preserve">شركة فليكسي للتأجير التمويلي</t>
   </si>
@@ -2760,597 +2760,600 @@
     <t xml:space="preserve">الدين البنكي</t>
   </si>
   <si>
+    <t xml:space="preserve">الرافعة المالية (المقام: صافي حقوق الملكية قبل خصومات CAR في مرحلة 4x؛ القاعدة الرأسمالية بعد الخصومات في مرحلة 9x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السقف التنظيمي المتوقع في نهاية السنة حسب خطة الترخيص</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هامش الرافعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة الرافعة في السيناريو المتوقع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأصول المرجحة بالمخاطر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWA الائتماني - صافي محفظة التأجير 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWA أصول تشغيلية أخرى 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILDC: الأقل من مجمل الربح أو 2.25% من متوسط الأصول المدرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC: الأكبر من إيرادات الخدمات أو المصروفات التشغيلية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FC: المكون المالي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مؤشر الأعمال BI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معامل BI المستخدم في الحالة الأساسية - مشتق من شريحة BI التخطيطية (راجع Basel III صف 96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مضاعف الخسارة الداخلية - افتراض</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مضاعف التحويل إلى RWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWA مخاطر التشغيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RWA مخاطر السوق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي RWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كفاية رأس المال CAR - تقدير تخطيطي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فائض/(فجوة) رأس المال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة CAR الرقابية النهائية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استرشادي - يتطلب اعتماد سجل الأصول/الخصومات ومعامل BI/ILM وبيانات السوق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التركز الائتماني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حد العميل الواحد والأطراف المرتبطة 30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حد داخلي استرشادي 25% من القاعدة الرأسمالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أكبر تعرض فعلي لعميل/أطراف مرتبطة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بيانات تشغيلية مطلوبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة التركز - اختبار 30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">افتراضات رقابية تخطيطية: وزن 100% لصافي محفظة التأجير والأصول التشغيلية؛ الخصم الحالي للأصول غير الملموسة Proxy مؤقت لحين سجل الأصول؛ معامل BI مشتق من شريحة BI التخطيطية في Basel III مع حساسية 15%/18%؛ ILM=1 مؤقتا لعدم وجود سجل خسائر؛ وRWA السوقية = صفر فقط مع افتراض عدم وجود محفظة تداول. لذلك CAR استرشادي وليس إقرار امتثال نهائيا.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شرائح رأس المال التنظيمي واحتياطيات رأس المال (وفق قرار 137/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشريحة الأولى الأساسية CET1 (= القاعدة بعد الخصومات؛ لا توجد أدوات AT1 مؤهلة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ الشريحة الأولى الإضافية AT1 (لا توجد أدوات مؤهلة حاليا)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي الشريحة الأولى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ الشريحة الثانية Tier 2 (دين تابع مؤهل - غير موجود حاليا)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي القاعدة الرأسمالية التنظيمية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة الشريحة الأولى الأساسية CET1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة الشريحة الأولى Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كفاية رأس المال الإجمالية CAR (تكرار من الصف 31 للمقارنة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحد الأدنى الأساسي (Pillar 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ احتياطي حماية رأس المال 2.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ الاحتياطي المعاكس للدورة الاقتصادية (0%-2.5%، يحدده مجلس إدارة الهيئة - لم يصدر تحديد بعد)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحد الأدنى الشامل للاحتياطيات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هامش/(فجوة) فوق الحد الشامل للاحتياطيات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحالة الشاملة للاحتياطيات - استرشادية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة: قرار 137/2025 يميز بين الشريحة الأولى (الأساسية) والشريحة الثانية (المساندة) واحتياطي حماية رأس المال 2.5% واحتياطي معاكس للدورة الاقتصادية 0%-2.5%؛ لا توجد لدى Flexy أدوات شريحة أولى إضافية (AT1) أو شريحة ثانية مؤهلة حاليا، فالشريحة الأولى الأساسية تساوي إجمالي رأس المال بعد الخصومات. قيمة الاحتياطي المعاكس للدورة الاقتصادية الفعلية تحددها الهيئة دوريا ولم تصدر بعد؛ استخدمت صفر مؤقتا.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جدول خصم الأصول غير الملموسة التفصيلي (بانتظار سجل الأصول الثابتة المعتمد)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الفئة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أجهزة وأثاث — ملموس، غير مقتطع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">برمجيات جاهزة (تراخيص استخدام) — غير ملموس، يقتطع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تطوير المنصة (برمجة داخلية/خارجية) — غير ملموس، يقتطع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التراخيص والتصاريح — غير ملموس، يقتطع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصروفات التأسيس — غير ملموس، يقتطع ما لم يعتمد خلاف ذلك</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة: بانتظار سجل الأصول الثابتة وغير الملموسة المعتمد وتأكيد مراقب الحسابات، يفترض النموذج مؤقتا أن 60% من صافي الأصول الثابتة/غير الملموسة تمثل أصولا غير ملموسة، ثم يخصم هذا الرصيد المقدر بالكامل بصورة متحفظة لأغراض CAR. هذا أكثر تحفظا من جدول الخصم الانتقالي الوارد بالقرار 137/2025، وسيستبدل بالتفصيل الفعلي ونسبة الخصم القانونية لكل فئة عند اعتماد سجل الأصول. Pending fixed-asset register and auditor validation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أصول ملموسة أخرى — ملموس، غير مقتطع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي الخصم التفصيلي (يستكمل عند توافر السجل)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة: بانتظار سجل الأصول الثابتة والاستثمارات المعتمد وتأكيد مراقب الحسابات، يستمر النموذج باستخدام الافتراض المتحفظ الحالي (خصم 60% من صافي الأصول الثابتة وغير الملموسة إجمالا - الصفوف 8-9 أعلاه) بدلا من هذا التفصيل الصفري مؤقتا؛ يجب استبدال هذا الافتراض بالتفصيل الفعلي عند اعتماد السجل وإعادة احتساب القاعدة الرأسمالية. Pending fixed-asset register and auditor validation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قياس معالجة فجوة سقف الاقتراض (خفض الدين أو زيادة القاعدة الرأسمالية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خفض الدين المطلوب للالتزام بالسقف الساري = MAX(0، الدين القائم - السقف الساري × المقام الصحيح لكل مرحلة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الزيادة المطلوبة في القاعدة الرأسمالية بديلا عن خفض الدين = MAX(0، الدين القائم ÷ السقف الساري - المقام الصحيح لكل مرحلة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة: القيمتان أعلاه بديلتان لبعضهما (تنفيذ أي منهما كاف لإغلاق فجوة الرافعة في السنة المعنية)، وتحسبان بالسقف الساري الفعلي لكل سنة (4× افتراضيا حتى تأكيد صدور الترخيص النهائي فعليا، أو 9× بعده) وليس برقم ثابت. راجع أيضا ورقتي Scenario - Slower Year 2 وScenario - Standby Capital كأداتين عمليتين لتنفيذ أي من الخيارين.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خطة التمويل والسيولة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصادر التمويل وتكلفته</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حد التسهيلات البنكية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رصيد الدين الختامي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السحوبات البنكية الإجمالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تكلفة الاقتراض</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العمر المرجح - سنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة تسهيل دوار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة تمويل متوسط الأجل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خدمة الدين السنوية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صافي السحب/(السداد) البنكي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اختبار تغطية السيولة لمدة 30 يوما</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأصول السائلة عالية الجودة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تدفقات نقدية خارجة خلال 30 يوما</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تدفقات نقدية داخلة خلال 30 يوما</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الحد الأقصى للاعتداد بالتدفقات الداخلة 90% (وفق النص النهائي لقرار 137/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صافي التدفقات الخارجة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة تغطية السيولة LCR - تقدير 30 يوما تخطيطي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة LCR (ليست نتيجة رقابية نهائية دون آجال تعاقدية فعلية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة صافي التمويل المستقر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القاعدة الرأسمالية لأغراض NSFR - وزن ASF 100% (قبل خصومات CAR-only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دين متبق ≥ سنة - وزن 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دين 6-12 شهر - وزن 75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دين أقل من 6 أشهر - وزن 50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي التمويل المستقر المتاح ASF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محفظة ≥ سنة - وزن 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محفظة 6-12 شهر - وزن 75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محفظة أقل من 6 أشهر - وزن 50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأصول التشغيلية - وزن 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي التمويل المستقر المطلوب RSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة صافي التمويل المستقر NSFR - تقدير تخطيطي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة NSFR (ليست نتيجة رقابية نهائية دون جداول آجال فعلية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة NSFR: وفق قرار 137/2025، خصومات CET1 المذكورة للأصول غير الملموسة وغيرها مخصصة لحساب كفاية رأس المال؛ لذلك يستخدم ASF هنا القاعدة الرأسمالية قبل خصومات CAR-only. تبقى أوزان آجال الدين والمحفظة تخطيطية لحين ورود الجداول التعاقدية الفعلية. المصدر: https://fra.gov.eg/wp-content/uploads/2025/08/alamiria_2025_137.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مفاضلة مصادر التمويل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الوزن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التوريق بعد التشغيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آلية الاختيار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التكلفة الإجمالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأقل تكلفة بعد الرسوم والتحوط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مطابقة الأجل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مطابقة عمر الالتزام بعمر العقد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرونة السحب والسداد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السحب حسب المنح والسداد من التحصيلات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الضمانات والتعهدات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أقل قيود مع الحفاظ على الامتثال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">البنوك المستهدفة مبدئيا: بنك مصر، البنك الأهلي المصري، بنك أبوظبي الأول، تنمية الصادرات وجهاز تنمية المشروعات. لا توجد عروض ملزمة حتى تاريخ إعداد الخطة؛ كل الحدود والأسعار والآجال افتراضات تخطيطية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اختبار الرافعة الشهري خلال Year 2 - السقف الساري 4x من صافي حقوق الملكية طوال الاثني عشر شهرا بالكامل (المرحلة المؤقتة قبل الترخيص النهائي وفق قرار 268/2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planning Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رأس المال المدفوع التراكمي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منه: الاحتياطي القانوني المؤهل (توزيع مؤقت خطي)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معلومة فقط: خصومات CAR التقديرية للأصول غير الملموسة — لا تخصم من صافي حقوق الملكية لاختبار 4× بقرار 268/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صافي حقوق الملكية لاختبار قرار 268/2023 = رأس المال المدفوع + الأرباح/(الخسائر) التراكمية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي القروض والتمويلات الخاضعة للسقف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مضاعف الرافعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السقف الساري</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هامش الأمان/(الفجوة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حالة الالتزام وفق سيناريو الترخيص المتوقع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مقارنة نهاية Year 2: السيناريو الملزم مقابل سيناريو غير جائز قانونا - للايضاح فقط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قاعدة القياس المستخدمة في نهاية Year 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي التمويل الخاضع للسقف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السقف المطبق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سيناريو غير جائز قانونا (توضيحي فقط): افتراض تطبيق 9x على القاعدة الرأسمالية التنظيمية خلال Year 2 رغم عدم جواز ذلك قبل صدور الترخيص النهائي فعليا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السيناريو الملزم الفعلي: 4x من صافي حقوق الملكية يسري طوال Year 2 بالكامل وفق المادة الثالثة من قرار 268/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة: القاعدة الملزمة طوال Year 1 وYear 2 هي 4x من صافي حقوق الملكية بصرف النظر عن الموعد المستهدف للترخيص. ارقام Year 2 المعتمدة بالخطة التجارية تؤدي فعليا الى مضاعف رافعة اعلى من 4x كما يظهر بالسيناريو الملزم اعلاه؛ راجع Regulatory Capital Plan صفوف 76-78 وScenario - Slower Year 2 وScenario - Standby Capital لمعالجة الفجوة دون تغيير ارقام الخطة التجارية المعتمدة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلم 30 يوما التخطيطي لـ LCR (يستخدم أفضل بيانات متاحة؛ بعض البنود متوسط شهري = الرقم السنوي ÷ 12 لحين ورود الاستحقاقات التعاقدية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نقدية وما في حكمها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ودائع بنكية مؤهلة (لا توجد حاليا)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أذون/سندات خزانة مؤهلة (لا توجد حاليا)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي الأصول السائلة عالية الجودة HQLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحصيلات مقدرة خلال 30 يوما (متوسط شهري من الخطة السنوية لحين جدول التحصيل التعاقدي)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سداد أصل الدين المقدر خلال 30 يوما (متوسط شهري من الخطة السنوية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تكلفة التمويل المقدرة خلال 30 يوما (متوسط شهري من الخطة السنوية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصروفات تشغيلية مقدرة خلال 30 يوما (متوسط شهري من الخطة السنوية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التزامات تعاقدية أخرى (سحوبات دين قصير الأجل متوقعة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي التدفقات الخارجة التعاقدية قبل الضغط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إضافة ضغط احترازي إضافي (حاليا صفر - بانتظار سياسة رسمية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إجمالي التدفقات الخارجة الإجمالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التدفقات الداخلة المؤهلة الفعلية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سقف الاعتداد بالتدفقات الداخلة 90% (وفق النص النهائي لقرار 137/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نسبة تغطية السيولة LCR (من التفصيل)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مطابقة مع الملخص أعلاه (يجب أن تساوي صفرا)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة: حساب LCR الحالي Proxy تخطيطي. النقدية مأخوذة من الرصيد الختامي، بينما التحصيلات وسداد أصل الدين وتكلفة التمويل والمصروفات تقرب إلى متوسط 30 يوما من الخطة السنوية عند غياب جدول تعاقدي أدق. لا يجوز اعتباره LCR رقابيا نهائيا قبل استبدال هذه التقديرات بعقود البنك وجدول تحصيل العقود الفعلي.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلم استحقاق صافي التمويل المستقر التفصيلي - Year 2 كمثال (يدعم صفوف 25-35 أعلاه)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القيمة الدفترية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الأجل المتبقي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معامل ASF/RSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القيمة المرجحة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصدر البيانات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فعلي/تخطيطي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القاعدة الرأسمالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;= سنة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory Capital Plan!C7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تخطيطي محسوب من النموذج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دين بنكي متبق سنة فأكثر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions!C102 (نسبة تخطيطية)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تخطيطي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دين بنكي 6-12 شهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-12 شهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">افتراض تخطيطي 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دين بنكي أقل من 6 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">افتراض تخطيطي (المتبقي)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">التزامات تشغيلية وتمويل مؤجل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6 أشهر (افتراض)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محفظة تأجير متبقية سنة فأكثر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;= سنة (افتراض)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">افتراض تخطيطي 70% (Sources A07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محفظة تأجير 6-12 شهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-12 شهر (افتراض)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">افتراض تخطيطي 20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محفظة تأجير أقل من 6 أشهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أصول تشغيلية أخرى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NSFR (من التفصيل)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة: معاملات ASF/RSF (100%/75%/50%) ونسب توزيع الآجال (70%/20%/10% وما شابه) لا تزال افتراضات تخطيطية موثقة في Sources A07 لعدم توافر عقود بنكية ملزمة وجدول استحقاق محفظة فعلي بعد. يجب تحديث هذا الجدول وإعادة احتساب NSFR عند ورود البيانات التعاقدية الفعلية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سيناريو: تباطؤ نمو Year 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الخطة الأصلية Year 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">السيناريو المعدل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملاحظة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">معامل تباطؤ النمو - نسبة من الخطة الأصلية (يطبق معا على المنح والتحصيلات والتمويل)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خلية زرقاء قابلة للتعديل - جرب أي نسبة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مؤشرات النشاط والتمويل المرتبط بها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عدد العقود التقديري</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رصيد المحفظة الإيجارية الختامي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رصيد Year 1 + (الإضافة الأصلية × المعامل)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رصيد الدين البنكي الختامي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يتحرك مع نفس معامل التمويل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الإيرادات والمصروفات - Year 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إيرادات خدمات مساندة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تكلفة العاملين (ثابتة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خطة توظيف ثابتة، لا تتأثر بالتباطؤ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المصروفات الإدارية والتشغيلية (ثابتة)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">الإهلاك والاستهلاك (ثابت)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صافي الربح بعد الضريبة؛ الضريبة في السيناريو = صفر لأن ربح ما قبل الضريبة المعدل لا يستنفد بالكامل خسائر Year 1 الضريبية المرحلة وفق افتراض التخطيط الحالي.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">القاعدة الرأسمالية والرافعة المالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رأس المال المدفوع (ثابت)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خطة المساهمين تعاقدية وغير مرتبطة بسرعة النمو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صافي حقوق الملكية لاختبار 4× وفق قرار 268/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لا تخصم خصومات CAR-only من مقام اختبار 4×</t>
+  </si>
+  <si>
     <t xml:space="preserve">الرافعة المالية</t>
   </si>
   <si>
-    <t xml:space="preserve">السقف التنظيمي المتوقع في نهاية السنة حسب خطة الترخيص</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هامش الرافعة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حالة الرافعة في السيناريو المتوقع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأصول المرجحة بالمخاطر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWA الائتماني - صافي محفظة التأجير 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWA أصول تشغيلية أخرى 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILDC: الأقل من مجمل الربح أو 2.25% من متوسط الأصول المدرة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC: الأكبر من إيرادات الخدمات أو المصروفات التشغيلية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FC: المكون المالي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مؤشر الأعمال BI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">معامل BI المستخدم في الحالة الأساسية - مشتق من شريحة BI التخطيطية (راجع Basel III صف 96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مضاعف الخسارة الداخلية - افتراض</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مضاعف التحويل إلى RWA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWA مخاطر التشغيل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RWA مخاطر السوق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي RWA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">كفاية رأس المال CAR - تقدير تخطيطي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فائض/(فجوة) رأس المال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حالة CAR الرقابية النهائية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استرشادي - يتطلب اعتماد سجل الأصول/الخصومات ومعامل BI/ILM وبيانات السوق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التركز الائتماني</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حد العميل الواحد والأطراف المرتبطة 30%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حد داخلي استرشادي 25% من القاعدة الرأسمالية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أكبر تعرض فعلي لعميل/أطراف مرتبطة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بيانات تشغيلية مطلوبة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حالة التركز - اختبار 30%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">افتراضات رقابية تخطيطية: وزن 100% لصافي محفظة التأجير والأصول التشغيلية؛ الخصم الحالي للأصول غير الملموسة Proxy مؤقت لحين سجل الأصول؛ معامل BI مشتق من شريحة BI التخطيطية في Basel III مع حساسية 15%/18%؛ ILM=1 مؤقتا لعدم وجود سجل خسائر؛ وRWA السوقية = صفر فقط مع افتراض عدم وجود محفظة تداول. لذلك CAR استرشادي وليس إقرار امتثال نهائيا.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شرائح رأس المال التنظيمي واحتياطيات رأس المال (وفق قرار 137/2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الشريحة الأولى الأساسية CET1 (= القاعدة بعد الخصومات؛ لا توجد أدوات AT1 مؤهلة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ الشريحة الأولى الإضافية AT1 (لا توجد أدوات مؤهلة حاليا)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي الشريحة الأولى</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ الشريحة الثانية Tier 2 (دين تابع مؤهل - غير موجود حاليا)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي القاعدة الرأسمالية التنظيمية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة الشريحة الأولى الأساسية CET1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة الشريحة الأولى Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">كفاية رأس المال الإجمالية CAR (تكرار من الصف 31 للمقارنة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحد الأدنى الأساسي (Pillar 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ احتياطي حماية رأس المال 2.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ الاحتياطي المعاكس للدورة الاقتصادية (0%-2.5%، يحدده مجلس إدارة الهيئة - لم يصدر تحديد بعد)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحد الأدنى الشامل للاحتياطيات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هامش/(فجوة) فوق الحد الشامل للاحتياطيات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحالة الشاملة للاحتياطيات - استرشادية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة: قرار 137/2025 يميز بين الشريحة الأولى (الأساسية) والشريحة الثانية (المساندة) واحتياطي حماية رأس المال 2.5% واحتياطي معاكس للدورة الاقتصادية 0%-2.5%؛ لا توجد لدى Flexy أدوات شريحة أولى إضافية (AT1) أو شريحة ثانية مؤهلة حاليا، فالشريحة الأولى الأساسية تساوي إجمالي رأس المال بعد الخصومات. قيمة الاحتياطي المعاكس للدورة الاقتصادية الفعلية تحددها الهيئة دوريا ولم تصدر بعد؛ استخدمت صفر مؤقتا.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جدول خصم الأصول غير الملموسة التفصيلي (بانتظار سجل الأصول الثابتة المعتمد)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الفئة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أجهزة وأثاث — ملموس، غير مقتطع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">برمجيات جاهزة (تراخيص استخدام) — غير ملموس، يقتطع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تطوير المنصة (برمجة داخلية/خارجية) — غير ملموس، يقتطع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التراخيص والتصاريح — غير ملموس، يقتطع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مصروفات التأسيس — غير ملموس، يقتطع ما لم يعتمد خلاف ذلك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة: بانتظار سجل الأصول الثابتة وغير الملموسة المعتمد وتأكيد مراقب الحسابات، يفترض النموذج مؤقتا أن 60% من صافي الأصول الثابتة/غير الملموسة تمثل أصولا غير ملموسة، ثم يخصم هذا الرصيد المقدر بالكامل بصورة متحفظة لأغراض CAR. هذا أكثر تحفظا من جدول الخصم الانتقالي الوارد بالقرار 137/2025، وسيستبدل بالتفصيل الفعلي ونسبة الخصم القانونية لكل فئة عند اعتماد سجل الأصول. Pending fixed-asset register and auditor validation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أصول ملموسة أخرى — ملموس، غير مقتطع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي الخصم التفصيلي (يستكمل عند توافر السجل)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة: بانتظار سجل الأصول الثابتة والاستثمارات المعتمد وتأكيد مراقب الحسابات، يستمر النموذج باستخدام الافتراض المتحفظ الحالي (خصم 60% من صافي الأصول الثابتة وغير الملموسة إجمالا - الصفوف 8-9 أعلاه) بدلا من هذا التفصيل الصفري مؤقتا؛ يجب استبدال هذا الافتراض بالتفصيل الفعلي عند اعتماد السجل وإعادة احتساب القاعدة الرأسمالية. Pending fixed-asset register and auditor validation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قياس معالجة فجوة سقف الاقتراض (خفض الدين أو زيادة القاعدة الرأسمالية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خفض الدين المطلوب للالتزام بالسقف الساري = MAX(0، الدين القائم - السقف الساري × القاعدة الرأسمالية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الزيادة المطلوبة في القاعدة الرأسمالية بديلا عن خفض الدين = MAX(0، الدين القائم ÷ السقف الساري - القاعدة الرأسمالية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة: القيمتان أعلاه بديلتان لبعضهما (تنفيذ أي منهما كاف لإغلاق فجوة الرافعة في السنة المعنية)، وتحسبان بالسقف الساري الفعلي لكل سنة (4× افتراضيا حتى تأكيد صدور الترخيص النهائي فعليا، أو 9× بعده) وليس برقم ثابت. راجع أيضا ورقتي Scenario - Slower Year 2 وScenario - Standby Capital كأداتين عمليتين لتنفيذ أي من الخيارين.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خطة التمويل والسيولة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مصادر التمويل وتكلفته</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حد التسهيلات البنكية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رصيد الدين الختامي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السحوبات البنكية الإجمالية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تكلفة الاقتراض</t>
-  </si>
-  <si>
-    <t xml:space="preserve">العمر المرجح - سنة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة تسهيل دوار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة تمويل متوسط الأجل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خدمة الدين السنوية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صافي السحب/(السداد) البنكي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اختبار تغطية السيولة لمدة 30 يوما</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأصول السائلة عالية الجودة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تدفقات نقدية خارجة خلال 30 يوما</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تدفقات نقدية داخلة خلال 30 يوما</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الحد الأقصى للاعتداد بالتدفقات الداخلة 90% (وفق النص النهائي لقرار 137/2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صافي التدفقات الخارجة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة تغطية السيولة LCR - تقدير 30 يوما تخطيطي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حالة LCR (ليست نتيجة رقابية نهائية دون آجال تعاقدية فعلية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة صافي التمويل المستقر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القاعدة الرأسمالية لأغراض NSFR - وزن ASF 100% (قبل خصومات CAR-only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دين متبق ≥ سنة - وزن 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دين 6-12 شهر - وزن 75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دين أقل من 6 أشهر - وزن 50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي التمويل المستقر المتاح ASF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محفظة ≥ سنة - وزن 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محفظة 6-12 شهر - وزن 75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محفظة أقل من 6 أشهر - وزن 50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأصول التشغيلية - وزن 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي التمويل المستقر المطلوب RSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة صافي التمويل المستقر NSFR - تقدير تخطيطي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حالة NSFR (ليست نتيجة رقابية نهائية دون جداول آجال فعلية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة NSFR: وفق قرار 137/2025، خصومات CET1 المذكورة للأصول غير الملموسة وغيرها مخصصة لحساب كفاية رأس المال؛ لذلك يستخدم ASF هنا القاعدة الرأسمالية قبل خصومات CAR-only. تبقى أوزان آجال الدين والمحفظة تخطيطية لحين ورود الجداول التعاقدية الفعلية. المصدر: https://fra.gov.eg/wp-content/uploads/2025/08/alamiria_2025_137.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مفاضلة مصادر التمويل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الوزن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التوريق بعد التشغيل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آلية الاختيار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التكلفة الإجمالية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأقل تكلفة بعد الرسوم والتحوط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مطابقة الأجل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مطابقة عمر الالتزام بعمر العقد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مرونة السحب والسداد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السحب حسب المنح والسداد من التحصيلات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الضمانات والتعهدات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أقل قيود مع الحفاظ على الامتثال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">البنوك المستهدفة مبدئيا: بنك مصر، البنك الأهلي المصري، بنك أبوظبي الأول، تنمية الصادرات وجهاز تنمية المشروعات. لا توجد عروض ملزمة حتى تاريخ إعداد الخطة؛ كل الحدود والأسعار والآجال افتراضات تخطيطية.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اختبار الرافعة الشهري خلال Year 2 - السقف الساري 4x من صافي حقوق الملكية طوال الاثني عشر شهرا بالكامل (المرحلة المؤقتة قبل الترخيص النهائي وفق قرار 268/2023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planning Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رأس المال المدفوع التراكمي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">منه: الاحتياطي القانوني المؤهل (توزيع مؤقت خطي)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">معلومة فقط: خصومات CAR التقديرية للأصول غير الملموسة — لا تخصم من صافي حقوق الملكية لاختبار 4× بقرار 268/2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صافي حقوق الملكية لاختبار قرار 268/2023 = رأس المال المدفوع + الأرباح/(الخسائر) التراكمية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي القروض والتمويلات الخاضعة للسقف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مضاعف الرافعة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السقف الساري</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هامش الأمان/(الفجوة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حالة الالتزام وفق سيناريو الترخيص المتوقع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مقارنة نهاية Year 2: السيناريو الملزم مقابل سيناريو غير جائز قانونا - للايضاح فقط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قاعدة القياس المستخدمة في نهاية Year 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي التمويل الخاضع للسقف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السقف المطبق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سيناريو غير جائز قانونا (توضيحي فقط): افتراض تطبيق 9x على القاعدة الرأسمالية التنظيمية خلال Year 2 رغم عدم جواز ذلك قبل صدور الترخيص النهائي فعليا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السيناريو الملزم الفعلي: 4x من صافي حقوق الملكية يسري طوال Year 2 بالكامل وفق المادة الثالثة من قرار 268/2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة: القاعدة الملزمة طوال Year 1 وYear 2 هي 4x من صافي حقوق الملكية بصرف النظر عن الموعد المستهدف للترخيص. ارقام Year 2 المعتمدة بالخطة التجارية تؤدي فعليا الى مضاعف رافعة اعلى من 4x كما يظهر بالسيناريو الملزم اعلاه؛ راجع Regulatory Capital Plan صفوف 76-78 وScenario - Slower Year 2 وScenario - Standby Capital لمعالجة الفجوة دون تغيير ارقام الخطة التجارية المعتمدة.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سلم 30 يوما التخطيطي لـ LCR (يستخدم أفضل بيانات متاحة؛ بعض البنود متوسط شهري = الرقم السنوي ÷ 12 لحين ورود الاستحقاقات التعاقدية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نقدية وما في حكمها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ودائع بنكية مؤهلة (لا توجد حاليا)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أذون/سندات خزانة مؤهلة (لا توجد حاليا)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي الأصول السائلة عالية الجودة HQLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تحصيلات مقدرة خلال 30 يوما (متوسط شهري من الخطة السنوية لحين جدول التحصيل التعاقدي)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سداد أصل الدين المقدر خلال 30 يوما (متوسط شهري من الخطة السنوية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تكلفة التمويل المقدرة خلال 30 يوما (متوسط شهري من الخطة السنوية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مصروفات تشغيلية مقدرة خلال 30 يوما (متوسط شهري من الخطة السنوية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التزامات تعاقدية أخرى (سحوبات دين قصير الأجل متوقعة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي التدفقات الخارجة التعاقدية قبل الضغط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إضافة ضغط احترازي إضافي (حاليا صفر - بانتظار سياسة رسمية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إجمالي التدفقات الخارجة الإجمالية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التدفقات الداخلة المؤهلة الفعلية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سقف الاعتداد بالتدفقات الداخلة 90% (وفق النص النهائي لقرار 137/2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نسبة تغطية السيولة LCR (من التفصيل)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مطابقة مع الملخص أعلاه (يجب أن تساوي صفرا)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة: حساب LCR الحالي Proxy تخطيطي. النقدية مأخوذة من الرصيد الختامي، بينما التحصيلات وسداد أصل الدين وتكلفة التمويل والمصروفات تقرب إلى متوسط 30 يوما من الخطة السنوية عند غياب جدول تعاقدي أدق. لا يجوز اعتباره LCR رقابيا نهائيا قبل استبدال هذه التقديرات بعقود البنك وجدول تحصيل العقود الفعلي.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سلم استحقاق صافي التمويل المستقر التفصيلي - Year 2 كمثال (يدعم صفوف 25-35 أعلاه)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القيمة الدفترية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الأجل المتبقي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">معامل ASF/RSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القيمة المرجحة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مصدر البيانات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فعلي/تخطيطي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القاعدة الرأسمالية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;= سنة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulatory Capital Plan!C7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تخطيطي محسوب من النموذج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دين بنكي متبق سنة فأكثر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions!C102 (نسبة تخطيطية)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تخطيطي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دين بنكي 6-12 شهر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-12 شهر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">افتراض تخطيطي 10%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دين بنكي أقل من 6 أشهر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6 أشهر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">افتراض تخطيطي (المتبقي)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">التزامات تشغيلية وتمويل مؤجل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6 أشهر (افتراض)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محفظة تأجير متبقية سنة فأكثر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;= سنة (افتراض)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">افتراض تخطيطي 70% (Sources A07)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محفظة تأجير 6-12 شهر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-12 شهر (افتراض)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">افتراض تخطيطي 20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محفظة تأجير أقل من 6 أشهر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أصول تشغيلية أخرى</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NSFR (من التفصيل)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة: معاملات ASF/RSF (100%/75%/50%) ونسب توزيع الآجال (70%/20%/10% وما شابه) لا تزال افتراضات تخطيطية موثقة في Sources A07 لعدم توافر عقود بنكية ملزمة وجدول استحقاق محفظة فعلي بعد. يجب تحديث هذا الجدول وإعادة احتساب NSFR عند ورود البيانات التعاقدية الفعلية.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سيناريو: تباطؤ نمو Year 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الخطة الأصلية Year 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">السيناريو المعدل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ملاحظة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">معامل تباطؤ النمو - نسبة من الخطة الأصلية (يطبق معا على المنح والتحصيلات والتمويل)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خلية زرقاء قابلة للتعديل - جرب أي نسبة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مؤشرات النشاط والتمويل المرتبط بها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عدد العقود التقديري</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رصيد المحفظة الإيجارية الختامي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رصيد Year 1 + (الإضافة الأصلية × المعامل)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رصيد الدين البنكي الختامي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">يتحرك مع نفس معامل التمويل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الإيرادات والمصروفات - Year 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إيرادات خدمات مساندة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تكلفة العاملين (ثابتة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خطة توظيف ثابتة، لا تتأثر بالتباطؤ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">المصروفات الإدارية والتشغيلية (ثابتة)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">الإهلاك والاستهلاك (ثابت)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صافي الربح بعد الضريبة؛ الضريبة في السيناريو = صفر لأن ربح ما قبل الضريبة المعدل لا يستنفد بالكامل خسائر Year 1 الضريبية المرحلة وفق افتراض التخطيط الحالي.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">القاعدة الرأسمالية والرافعة المالية</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رأس المال المدفوع (ثابت)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خطة المساهمين تعاقدية وغير مرتبطة بسرعة النمو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صافي حقوق الملكية لاختبار 4× وفق قرار 268/2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لا تخصم خصومات CAR-only من مقام اختبار 4×</t>
-  </si>
-  <si>
     <t xml:space="preserve">الدين ÷ صافي حقوق الملكية</t>
   </si>
   <si>
@@ -3882,7 +3885,7 @@
     <t xml:space="preserve">رصيد الدين البنكي القائم</t>
   </si>
   <si>
-    <t xml:space="preserve">÷ القاعدة الرأسمالية بعد الخصومات</t>
+    <t xml:space="preserve">÷ المقام الصحيح (صافي حقوق الملكية قبل خصومات CAR في مرحلة 4x؛ القاعدة بعد الخصومات في مرحلة 9x)</t>
   </si>
   <si>
     <t xml:space="preserve">= مضاعف الاقتراض الرقابي المحقق / Achieved FRA Borrowing Multiple</t>
@@ -20669,7 +20672,7 @@
       </c>
       <c r="C18" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!C13</f>
-        <v>5.05426192003465</v>
+        <v>4.86287064177048</v>
       </c>
       <c r="D18" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!D13</f>
@@ -24674,23 +24677,23 @@
         <v>902</v>
       </c>
       <c r="B13" s="301" t="n">
-        <f aca="false">IFERROR(B12/B10,0)</f>
+        <f aca="false">IFERROR(B12/IF(B14=9,B10,B7),0)</f>
         <v>0</v>
       </c>
       <c r="C13" s="301" t="n">
-        <f aca="false">IFERROR(C12/C10,0)</f>
-        <v>5.05426192003465</v>
+        <f aca="false">IFERROR(C12/IF(C14=9,C10,C7),0)</f>
+        <v>4.86287064177048</v>
       </c>
       <c r="D13" s="301" t="n">
-        <f aca="false">IFERROR(D12/D10,0)</f>
+        <f aca="false">IFERROR(D12/IF(D14=9,D10,D7),0)</f>
         <v>4.56798051102073</v>
       </c>
       <c r="E13" s="301" t="n">
-        <f aca="false">IFERROR(E12/E10,0)</f>
+        <f aca="false">IFERROR(E12/IF(E14=9,E10,E7),0)</f>
         <v>4.30787332942035</v>
       </c>
       <c r="F13" s="301" t="n">
-        <f aca="false">IFERROR(F12/F10,0)</f>
+        <f aca="false">IFERROR(F12/IF(F14=9,F10,F7),0)</f>
         <v>4.33580712139099</v>
       </c>
     </row>
@@ -24729,7 +24732,7 @@
       </c>
       <c r="C15" s="301" t="n">
         <f aca="false">C14-C13</f>
-        <v>-1.05426192003465</v>
+        <v>-0.862870641770479</v>
       </c>
       <c r="D15" s="301" t="n">
         <f aca="false">D14-D13</f>
@@ -25904,23 +25907,23 @@
         <v>958</v>
       </c>
       <c r="B76" s="287" t="n">
-        <f aca="false">MAX(0,B12-B14*B10)</f>
+        <f aca="false">MAX(0,B12-B14*IF(B14=9,B10,B7))</f>
         <v>0</v>
       </c>
       <c r="C76" s="287" t="n">
-        <f aca="false">MAX(0,C12-C14*C10)</f>
-        <v>77177818.7566001</v>
+        <f aca="false">MAX(0,C12-C14*IF(C14=9,C10,C7))</f>
+        <v>65653018.7566001</v>
       </c>
       <c r="D76" s="287" t="n">
-        <f aca="false">MAX(0,D12-D14*D10)</f>
+        <f aca="false">MAX(0,D12-D14*IF(D14=9,D10,D7))</f>
         <v>0</v>
       </c>
       <c r="E76" s="287" t="n">
-        <f aca="false">MAX(0,E12-E14*E10)</f>
+        <f aca="false">MAX(0,E12-E14*IF(E14=9,E10,E7))</f>
         <v>0</v>
       </c>
       <c r="F76" s="287" t="n">
-        <f aca="false">MAX(0,F12-F14*F10)</f>
+        <f aca="false">MAX(0,F12-F14*IF(F14=9,F10,F7))</f>
         <v>0</v>
       </c>
     </row>
@@ -25929,23 +25932,23 @@
         <v>959</v>
       </c>
       <c r="B77" s="287" t="n">
-        <f aca="false">MAX(0,B12/B14-B10)</f>
+        <f aca="false">MAX(0,B12/B14-IF(B14=9,B10,B7))</f>
         <v>0</v>
       </c>
       <c r="C77" s="287" t="n">
-        <f aca="false">MAX(0,C12/C14-C10)</f>
-        <v>19294454.68915</v>
+        <f aca="false">MAX(0,C12/C14-IF(C14=9,C10,C7))</f>
+        <v>16413254.68915</v>
       </c>
       <c r="D77" s="287" t="n">
-        <f aca="false">MAX(0,D12/D14-D10)</f>
+        <f aca="false">MAX(0,D12/D14-IF(D14=9,D10,D7))</f>
         <v>0</v>
       </c>
       <c r="E77" s="287" t="n">
-        <f aca="false">MAX(0,E12/E14-E10)</f>
+        <f aca="false">MAX(0,E12/E14-IF(E14=9,E10,E7))</f>
         <v>0</v>
       </c>
       <c r="F77" s="287" t="n">
-        <f aca="false">MAX(0,F12/F14-F10)</f>
+        <f aca="false">MAX(0,F12/F14-IF(F14=9,F10,F7))</f>
         <v>0</v>
       </c>
     </row>
@@ -28752,7 +28755,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="286" t="s">
-        <v>902</v>
+        <v>1099</v>
       </c>
       <c r="B27" s="301" t="n">
         <f aca="false">B11/B26</f>
@@ -28763,12 +28766,12 @@
         <v>4.52234373046079</v>
       </c>
       <c r="D27" s="286" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="286" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B28" s="301" t="n">
         <f aca="false">4</f>
@@ -28779,7 +28782,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="286" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28798,7 +28801,7 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="337" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B31" s="337"/>
       <c r="C31" s="337"/>
@@ -28806,7 +28809,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="286" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B32" s="287" t="n">
         <f aca="false">'Cash Flow'!B25</f>
@@ -28834,7 +28837,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="286" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B34" s="287" t="n">
         <f aca="false">'Cash Flow'!C15</f>
@@ -28848,7 +28851,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="286" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B35" s="287" t="n">
         <f aca="false">'Cash Flow'!C21</f>
@@ -28859,7 +28862,7 @@
         <v>374300000</v>
       </c>
       <c r="D35" s="286" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28892,7 +28895,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="286" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B38" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!C17</f>
@@ -28906,7 +28909,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="286" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B39" s="287" t="n">
         <f aca="false">MIN('Funding &amp; Liquidity'!C18,'Funding &amp; Liquidity'!C19)</f>
@@ -28948,7 +28951,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="286" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B42" s="286" t="str">
         <f aca="false">IF(B41&gt;=1,"استرشادي - بيانات آجال تعاقدية مطلوبة","فجوة تخطيطية")</f>
@@ -28962,7 +28965,7 @@
     </row>
     <row r="44" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="304" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B44" s="304"/>
       <c r="C44" s="304"/>
@@ -28970,7 +28973,7 @@
     </row>
     <row r="46" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="304" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B46" s="304"/>
       <c r="C46" s="304"/>
@@ -28978,7 +28981,7 @@
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="27" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B48" s="27"/>
       <c r="C48" s="27"/>
@@ -28986,7 +28989,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="286" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B49" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!C19</f>
@@ -28999,7 +29002,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="286" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B50" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!C28</f>
@@ -29010,12 +29013,12 @@
         <v>63134412.3694719</v>
       </c>
       <c r="D50" s="286" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="286" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B51" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!C30</f>
@@ -29028,7 +29031,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="286" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B52" s="293" t="n">
         <f aca="false">'Regulatory Capital Plan'!C31</f>
@@ -29041,7 +29044,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="286" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B53" s="286" t="str">
         <f aca="false">IF(B52&gt;=12%,"استرشادي - اعتماد مدخلات رقابية مطلوب","فجوة تخطيطية")</f>
@@ -29054,7 +29057,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="286" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B55" s="293" t="n">
         <f aca="false">'Funding &amp; Liquidity'!C35</f>
@@ -29067,7 +29070,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="286" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B56" s="286" t="str">
         <f aca="false">IF(B55&gt;=100%,"استرشادي - بيانات آجال تعاقدية مطلوبة","فجوة تخطيطية")</f>
@@ -29080,7 +29083,7 @@
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="304" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B58" s="304"/>
       <c r="C58" s="304"/>
@@ -29119,7 +29122,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="283" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -29130,10 +29133,10 @@
         <v>83</v>
       </c>
       <c r="B3" s="284" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C3" s="284" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D3" s="284" t="s">
         <v>1078</v>
@@ -29141,19 +29144,19 @@
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="286" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B4" s="286"/>
       <c r="C4" s="66" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="286" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="337" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B6" s="337"/>
       <c r="C6" s="337"/>
@@ -29161,7 +29164,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="286" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B7" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!C12</f>
@@ -29172,12 +29175,12 @@
         <v>370000000</v>
       </c>
       <c r="D7" s="286" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="286" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B8" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!C10</f>
@@ -29188,12 +29191,12 @@
         <v>76086745.31085</v>
       </c>
       <c r="D8" s="286" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="337" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B10" s="337"/>
       <c r="C10" s="337"/>
@@ -29201,7 +29204,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="286" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B11" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!C14</f>
@@ -29212,12 +29215,12 @@
         <v>4</v>
       </c>
       <c r="D11" s="286" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="286" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B12" s="301" t="n">
         <f aca="false">B7/B8</f>
@@ -29228,12 +29231,12 @@
         <v>4.86287064177048</v>
       </c>
       <c r="D12" s="286" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="286" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B13" s="286" t="str">
         <f aca="false">IF(B12&lt;=B11,"متوافق","فجوة")</f>
@@ -29247,7 +29250,7 @@
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="337" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B15" s="337"/>
       <c r="C15" s="337"/>
@@ -29255,7 +29258,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="286" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B16" s="287" t="n">
         <f aca="false">B7/B11</f>
@@ -29266,12 +29269,12 @@
         <v>92500000</v>
       </c>
       <c r="D16" s="286" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="286" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B17" s="287" t="n">
         <f aca="false">MAX(0,B16-B8)</f>
@@ -29285,7 +29288,7 @@
     </row>
     <row r="18" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="304" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B18" s="287" t="n">
         <f aca="false">B17</f>
@@ -29299,7 +29302,7 @@
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="304" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B19" s="67" t="n">
         <v>0</v>
@@ -29309,12 +29312,12 @@
         <v>16413254.68915</v>
       </c>
       <c r="D19" s="304" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="113" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B20" s="113"/>
       <c r="C20" s="113" t="n">
@@ -29322,12 +29325,12 @@
         <v>65653018.7566001</v>
       </c>
       <c r="D20" s="113" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="337" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B21" s="337"/>
       <c r="C21" s="337"/>
@@ -29335,7 +29338,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="286" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B22" s="287" t="n">
         <f aca="false">B8+B19</f>
@@ -29349,7 +29352,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="286" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B23" s="301" t="n">
         <f aca="false">B7/B22</f>
@@ -29363,7 +29366,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="286" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B24" s="286" t="str">
         <f aca="false">IF(B23&lt;=B11,"متوافق","فجوة")</f>
@@ -29377,7 +29380,7 @@
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="337" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B26" s="337"/>
       <c r="C26" s="337"/>
@@ -29385,7 +29388,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="286" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B27" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!C16</f>
@@ -29399,7 +29402,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="286" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B28" s="287" t="n">
         <f aca="false">B27+B19</f>
@@ -29413,7 +29416,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="286" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B29" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!C20</f>
@@ -29427,7 +29430,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="286" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B30" s="292" t="n">
         <f aca="false">B27/B29</f>
@@ -29441,7 +29444,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="286" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B31" s="292" t="n">
         <f aca="false">B28/B29</f>
@@ -29452,12 +29455,12 @@
         <v>3.01992583389569</v>
       </c>
       <c r="D31" s="286" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="286" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B32" s="286" t="str">
         <f aca="false">IF(B31&gt;=1,"استرشادي - بيانات آجال تعاقدية مطلوبة","فجوة تخطيطية")</f>
@@ -29471,7 +29474,7 @@
     </row>
     <row r="34" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="304" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B34" s="304"/>
       <c r="C34" s="304"/>
@@ -29479,7 +29482,7 @@
     </row>
     <row r="36" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="304" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B36" s="304"/>
       <c r="C36" s="304"/>
@@ -29487,7 +29490,7 @@
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="27" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B38" s="27"/>
       <c r="C38" s="27"/>
@@ -29495,7 +29498,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B39" s="293" t="n">
         <f aca="false">'Regulatory Capital Plan'!C31</f>
@@ -29508,7 +29511,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B40" s="293" t="n">
         <f aca="false">('Regulatory Capital Plan'!C10+B19)/'Regulatory Capital Plan'!$C$30</f>
@@ -29521,7 +29524,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="286" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B41" s="286" t="str">
         <f aca="false">IF(B40&gt;=12%,"استرشادي - اعتماد مدخلات رقابية مطلوب","فجوة تخطيطية")</f>
@@ -29534,7 +29537,7 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B43" s="27"/>
       <c r="C43" s="27"/>
@@ -29542,7 +29545,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="286" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B44" s="286"/>
       <c r="C44" s="286"/>
@@ -31779,7 +31782,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="310" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B1" s="310"/>
       <c r="C1" s="310"/>
@@ -31793,16 +31796,16 @@
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="315" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B3" s="315" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C3" s="315" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D3" s="315" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31813,7 +31816,7 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="338" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B5" s="338"/>
       <c r="C5" s="338"/>
@@ -31824,10 +31827,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="340" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C6" s="340" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D6" s="341" t="s">
         <v>40</v>
@@ -31838,10 +31841,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="340" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C7" s="340" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D7" s="341" t="s">
         <v>42</v>
@@ -31852,10 +31855,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="340" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C8" s="340" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D8" s="341" t="s">
         <v>44</v>
@@ -31866,10 +31869,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="340" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C9" s="340" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D9" s="341" t="s">
         <v>20</v>
@@ -31880,10 +31883,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="340" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C10" s="340" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D10" s="341" t="s">
         <v>20</v>
@@ -31894,10 +31897,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="340" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C11" s="340" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D11" s="341" t="s">
         <v>28</v>
@@ -31908,10 +31911,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="340" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C12" s="340" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D12" s="341" t="s">
         <v>26</v>
@@ -31925,7 +31928,7 @@
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="338" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B14" s="338"/>
       <c r="C14" s="338"/>
@@ -31936,10 +31939,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="340" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C15" s="340" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D15" s="341" t="s">
         <v>22</v>
@@ -31950,10 +31953,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="340" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C16" s="340" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D16" s="341" t="s">
         <v>22</v>
@@ -31964,10 +31967,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="340" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C17" s="340" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D17" s="341" t="s">
         <v>22</v>
@@ -31978,10 +31981,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="340" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C18" s="340" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D18" s="341" t="s">
         <v>48</v>
@@ -31992,10 +31995,10 @@
         <v>12</v>
       </c>
       <c r="B19" s="340" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C19" s="340" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D19" s="341" t="s">
         <v>68</v>
@@ -32006,10 +32009,10 @@
         <v>13</v>
       </c>
       <c r="B20" s="340" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C20" s="340" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D20" s="341" t="s">
         <v>68</v>
@@ -32020,10 +32023,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="340" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C21" s="340" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D21" s="341" t="s">
         <v>22</v>
@@ -32034,10 +32037,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="340" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C22" s="340" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="D22" s="341" t="s">
         <v>46</v>
@@ -32048,10 +32051,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="340" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C23" s="340" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D23" s="341" t="s">
         <v>30</v>
@@ -32065,7 +32068,7 @@
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="338" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B25" s="338"/>
       <c r="C25" s="338"/>
@@ -32076,10 +32079,10 @@
         <v>17</v>
       </c>
       <c r="B26" s="340" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C26" s="340" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D26" s="341" t="s">
         <v>48</v>
@@ -32090,10 +32093,10 @@
         <v>18</v>
       </c>
       <c r="B27" s="340" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C27" s="340" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D27" s="341" t="s">
         <v>48</v>
@@ -32104,10 +32107,10 @@
         <v>19</v>
       </c>
       <c r="B28" s="340" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C28" s="340" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="D28" s="341" t="s">
         <v>48</v>
@@ -32118,10 +32121,10 @@
         <v>20</v>
       </c>
       <c r="B29" s="340" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C29" s="340" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D29" s="341" t="s">
         <v>48</v>
@@ -32132,10 +32135,10 @@
         <v>21</v>
       </c>
       <c r="B30" s="340" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C30" s="340" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D30" s="341" t="s">
         <v>48</v>
@@ -32146,10 +32149,10 @@
         <v>22</v>
       </c>
       <c r="B31" s="340" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="C31" s="340" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D31" s="341" t="s">
         <v>48</v>
@@ -32160,10 +32163,10 @@
         <v>23</v>
       </c>
       <c r="B32" s="340" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C32" s="340" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D32" s="341" t="s">
         <v>48</v>
@@ -32174,10 +32177,10 @@
         <v>24</v>
       </c>
       <c r="B33" s="340" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="C33" s="340" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D33" s="341" t="s">
         <v>56</v>
@@ -32188,10 +32191,10 @@
         <v>25</v>
       </c>
       <c r="B34" s="340" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="C34" s="340" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="D34" s="341" t="s">
         <v>54</v>
@@ -32202,10 +32205,10 @@
         <v>26</v>
       </c>
       <c r="B35" s="340" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C35" s="340" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D35" s="341" t="s">
         <v>52</v>
@@ -32219,7 +32222,7 @@
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="338" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B37" s="338"/>
       <c r="C37" s="338"/>
@@ -32230,10 +32233,10 @@
         <v>27</v>
       </c>
       <c r="B38" s="340" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C38" s="340" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D38" s="341" t="s">
         <v>50</v>
@@ -32244,10 +32247,10 @@
         <v>28</v>
       </c>
       <c r="B39" s="340" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C39" s="340" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D39" s="341" t="s">
         <v>50</v>
@@ -32258,10 +32261,10 @@
         <v>29</v>
       </c>
       <c r="B40" s="340" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C40" s="340" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D40" s="341" t="s">
         <v>50</v>
@@ -32272,10 +32275,10 @@
         <v>30</v>
       </c>
       <c r="B41" s="340" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C41" s="340" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D41" s="341" t="s">
         <v>50</v>
@@ -32286,10 +32289,10 @@
         <v>31</v>
       </c>
       <c r="B42" s="340" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C42" s="340" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D42" s="341" t="s">
         <v>66</v>
@@ -32300,10 +32303,10 @@
         <v>32</v>
       </c>
       <c r="B43" s="340" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="C43" s="340" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D43" s="341" t="s">
         <v>70</v>
@@ -32314,10 +32317,10 @@
         <v>33</v>
       </c>
       <c r="B44" s="340" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C44" s="340" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D44" s="341" t="s">
         <v>72</v>
@@ -32331,7 +32334,7 @@
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="338" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B46" s="338"/>
       <c r="C46" s="338"/>
@@ -32342,10 +32345,10 @@
         <v>34</v>
       </c>
       <c r="B47" s="340" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C47" s="340" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="D47" s="341" t="s">
         <v>26</v>
@@ -32359,7 +32362,7 @@
     </row>
     <row r="49" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="343" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B49" s="343"/>
       <c r="C49" s="343"/>
@@ -32469,7 +32472,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="283" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B1" s="283"/>
       <c r="C1" s="283"/>
@@ -32534,7 +32537,7 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="348" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B6" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B5</f>
@@ -32559,7 +32562,7 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="348" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B7" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B6</f>
@@ -32584,7 +32587,7 @@
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="348" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B8" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B7</f>
@@ -32609,7 +32612,7 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="348" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B9" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B8</f>
@@ -32634,7 +32637,7 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="348" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B10" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B10</f>
@@ -32684,7 +32687,7 @@
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="347" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B13" s="337"/>
       <c r="C13" s="337"/>
@@ -32694,7 +32697,7 @@
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="348" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B14" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B19</f>
@@ -32719,7 +32722,7 @@
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="348" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B15" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B20</f>
@@ -32744,7 +32747,7 @@
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="348" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B16" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B19+'Regulatory Capital Plan'!B20</f>
@@ -32769,7 +32772,7 @@
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="347" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B18" s="337"/>
       <c r="C18" s="337"/>
@@ -32779,7 +32782,7 @@
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="348" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B19" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B21</f>
@@ -32804,7 +32807,7 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="348" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B20" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B22</f>
@@ -32829,7 +32832,7 @@
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="348" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B21" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B23</f>
@@ -32854,7 +32857,7 @@
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="348" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B22" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B24</f>
@@ -32879,7 +32882,7 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="348" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B23" s="292" t="n">
         <f aca="false">B96</f>
@@ -32904,7 +32907,7 @@
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="348" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B24" s="301" t="n">
         <f aca="false">1</f>
@@ -32929,7 +32932,7 @@
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="348" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B25" s="301" t="n">
         <f aca="false">Assumptions!B97</f>
@@ -32954,7 +32957,7 @@
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="348" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B26" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B28</f>
@@ -32979,7 +32982,7 @@
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="347" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B28" s="337"/>
       <c r="C28" s="337"/>
@@ -32989,7 +32992,7 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="348" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B29" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B29</f>
@@ -33014,7 +33017,7 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="347" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B31" s="337"/>
       <c r="C31" s="337"/>
@@ -33024,7 +33027,7 @@
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="348" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B32" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B30</f>
@@ -33049,7 +33052,7 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="348" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B33" s="292" t="n">
         <f aca="false">'Regulatory Capital Plan'!B31</f>
@@ -33074,7 +33077,7 @@
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="348" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B34" s="292" t="n">
         <f aca="false">Assumptions!B95</f>
@@ -33099,7 +33102,7 @@
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="348" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B35" s="292" t="n">
         <f aca="false">'Regulatory Capital Plan'!B31-'Regulatory Capital Plan'!B32</f>
@@ -33124,7 +33127,7 @@
     </row>
     <row r="36" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="348" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B36" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B33</f>
@@ -33149,7 +33152,7 @@
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="348" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B37" s="286" t="str">
         <f aca="false">IF(B33&lt;12%,"فجوة تخطيطية","استرشادي - يحتاج اعتماد مدخلات القاعدة/BI/ILM")</f>
@@ -33174,7 +33177,7 @@
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="347" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B39" s="337"/>
       <c r="C39" s="337"/>
@@ -33184,7 +33187,7 @@
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="348" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B40" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B12</f>
@@ -33209,32 +33212,32 @@
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="348" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B41" s="287" t="n">
-        <f aca="false">'Regulatory Capital Plan'!B10</f>
-        <v>19251929.2373</v>
+        <f aca="false">IF('Regulatory Capital Plan'!B14=9,'Regulatory Capital Plan'!B10,'Regulatory Capital Plan'!B7)</f>
+        <v>21833129.2373</v>
       </c>
       <c r="C41" s="287" t="n">
-        <f aca="false">'Regulatory Capital Plan'!C10</f>
-        <v>73205545.31085</v>
+        <f aca="false">IF('Regulatory Capital Plan'!C14=9,'Regulatory Capital Plan'!C10,'Regulatory Capital Plan'!C7)</f>
+        <v>76086745.31085</v>
       </c>
       <c r="D41" s="287" t="n">
-        <f aca="false">'Regulatory Capital Plan'!D10</f>
+        <f aca="false">IF('Regulatory Capital Plan'!D14=9,'Regulatory Capital Plan'!D10,'Regulatory Capital Plan'!D7)</f>
         <v>149956856.94091</v>
       </c>
       <c r="E41" s="287" t="n">
-        <f aca="false">'Regulatory Capital Plan'!E10</f>
+        <f aca="false">IF('Regulatory Capital Plan'!E14=9,'Regulatory Capital Plan'!E10,'Regulatory Capital Plan'!E7)</f>
         <v>309897691.485658</v>
       </c>
       <c r="F41" s="287" t="n">
-        <f aca="false">'Regulatory Capital Plan'!F10</f>
+        <f aca="false">IF('Regulatory Capital Plan'!F14=9,'Regulatory Capital Plan'!F10,'Regulatory Capital Plan'!F7)</f>
         <v>599657670.926534</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="348" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B42" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!B13</f>
@@ -33242,7 +33245,7 @@
       </c>
       <c r="C42" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!C13</f>
-        <v>5.05426192003465</v>
+        <v>4.86287064177048</v>
       </c>
       <c r="D42" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!D13</f>
@@ -33259,7 +33262,7 @@
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="348" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B43" s="301" t="n">
         <f aca="false">Assumptions!B51</f>
@@ -33309,7 +33312,7 @@
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="286" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B45" s="286"/>
       <c r="C45" s="286"/>
@@ -33319,7 +33322,7 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="349" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B47" s="349"/>
       <c r="C47" s="349"/>
@@ -33329,7 +33332,7 @@
     </row>
     <row r="48" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="350" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B48" s="350"/>
       <c r="C48" s="350"/>
@@ -33339,7 +33342,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="351" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B49" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B10</f>
@@ -33364,7 +33367,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="352" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B50" s="287" t="n">
         <f aca="false">'Balance Sheet'!B11</f>
@@ -33389,7 +33392,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="352" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B51" s="287" t="n">
         <f aca="false">Assumptions!B121*Assumptions!B107</f>
@@ -33414,7 +33417,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="352" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B52" s="287" t="n">
         <f aca="false">Assumptions!B124</f>
@@ -33439,7 +33442,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="352" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B53" s="287" t="n">
         <f aca="false">SUM(B50:B52)</f>
@@ -33464,7 +33467,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="352" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B54" s="292" t="n">
         <f aca="false">IFERROR(B49/B53,0)</f>
@@ -33489,7 +33492,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="351" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B55" s="292" t="n">
         <v>0.03</v>
@@ -33509,7 +33512,7 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="351" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B56" s="286" t="str">
         <f aca="false">IF(B54&gt;=B55,"متوافق استرشاديا بشرط تأكيد الانكشافات خارج الميزانية","فجوة")</f>
@@ -33534,7 +33537,7 @@
     </row>
     <row r="57" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="353" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B57" s="353"/>
       <c r="C57" s="353"/>
@@ -33544,7 +33547,7 @@
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="347" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B59" s="337"/>
       <c r="C59" s="337"/>
@@ -33554,7 +33557,7 @@
     </row>
     <row r="60" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="348" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B60" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B16</f>
@@ -33579,7 +33582,7 @@
     </row>
     <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="348" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B61" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B17</f>
@@ -33604,7 +33607,7 @@
     </row>
     <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="348" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B62" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B18</f>
@@ -33654,7 +33657,7 @@
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="348" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B64" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B20</f>
@@ -33679,7 +33682,7 @@
     </row>
     <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="348" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B65" s="292" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B21</f>
@@ -33704,7 +33707,7 @@
     </row>
     <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="348" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B66" s="292" t="n">
         <f aca="false">1</f>
@@ -33754,7 +33757,7 @@
     </row>
     <row r="69" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="347" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B69" s="337"/>
       <c r="C69" s="337"/>
@@ -33764,7 +33767,7 @@
     </row>
     <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="348" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B70" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B25</f>
@@ -33789,7 +33792,7 @@
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="348" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B71" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B26</f>
@@ -33814,7 +33817,7 @@
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="348" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B72" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B27</f>
@@ -33839,7 +33842,7 @@
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="348" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B73" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B28</f>
@@ -33864,7 +33867,7 @@
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="348" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B74" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B29</f>
@@ -33889,7 +33892,7 @@
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="348" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B75" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B30</f>
@@ -33914,7 +33917,7 @@
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="348" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B76" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B31</f>
@@ -33939,7 +33942,7 @@
     </row>
     <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="348" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B77" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B32</f>
@@ -33964,7 +33967,7 @@
     </row>
     <row r="78" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="348" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B78" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B33</f>
@@ -33989,7 +33992,7 @@
     </row>
     <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="348" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B79" s="287" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B34</f>
@@ -34014,7 +34017,7 @@
     </row>
     <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="348" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B80" s="292" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B35</f>
@@ -34039,7 +34042,7 @@
     </row>
     <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="348" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B81" s="292" t="n">
         <f aca="false">1</f>
@@ -34089,7 +34092,7 @@
     </row>
     <row r="84" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="347" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B84" s="337"/>
       <c r="C84" s="337"/>
@@ -34099,7 +34102,7 @@
     </row>
     <row r="85" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="348" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B85" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B36</f>
@@ -34124,7 +34127,7 @@
     </row>
     <row r="86" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="348" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B86" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B37</f>
@@ -34149,7 +34152,7 @@
     </row>
     <row r="87" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="348" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B87" s="287" t="str">
         <f aca="false">'Regulatory Capital Plan'!B38</f>
@@ -34199,7 +34202,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="354" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B90" s="354"/>
       <c r="C90" s="354"/>
@@ -34229,7 +34232,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="348" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B92" s="287" t="n">
         <f aca="false">'Regulatory Capital Plan'!B24</f>
@@ -34254,7 +34257,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="348" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B93" s="287" t="n">
         <f aca="false">B92</f>
@@ -34279,7 +34282,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="348" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B94" s="287" t="n">
         <v>1000000000</v>
@@ -34299,7 +34302,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="348" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B95" s="287" t="n">
         <v>30000000000</v>
@@ -34319,7 +34322,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="348" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B96" s="292" t="n">
         <f aca="false">IF(B93&lt;=B94,12%,IF(B93&lt;=B95,15%,18%))</f>
@@ -34344,7 +34347,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="353" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B97" s="353"/>
       <c r="C97" s="353"/>
@@ -34354,7 +34357,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="354" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B99" s="354"/>
       <c r="C99" s="354"/>
@@ -34384,7 +34387,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="348" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B101" s="287" t="n">
         <v>0</v>
@@ -34404,7 +34407,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="348" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B102" s="287" t="n">
         <v>0</v>
@@ -34424,7 +34427,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="348" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B103" s="287" t="n">
         <f aca="false">15*B102</f>
@@ -34452,24 +34455,24 @@
         <v>1048</v>
       </c>
       <c r="B104" s="348" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C104" s="348" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D104" s="348" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="E104" s="348" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="F104" s="348" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="348" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B105" s="287" t="n">
         <v>1</v>
@@ -34489,7 +34492,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="354" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B107" s="354"/>
       <c r="C107" s="354"/>
@@ -34505,37 +34508,37 @@
     </row>
     <row r="108" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="348" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B108" s="348" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C108" s="348" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D108" s="348" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="E108" s="348" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="F108" s="348" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="G108" s="348" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H108" s="348" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="I108" s="348" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="J108" s="348" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="K108" s="348" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="L108" s="348" t="s">
         <v>657</v>
@@ -34569,7 +34572,7 @@
         <v>0.25</v>
       </c>
       <c r="K109" s="287" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34600,7 +34603,7 @@
         <v>0.25</v>
       </c>
       <c r="K110" s="287" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34631,7 +34634,7 @@
         <v>0.25</v>
       </c>
       <c r="K111" s="287" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34662,7 +34665,7 @@
         <v>0.25</v>
       </c>
       <c r="K112" s="287" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34693,12 +34696,12 @@
         <v>0.25</v>
       </c>
       <c r="K113" s="287" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="348" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="G114" s="287" t="n">
         <f aca="false">MAX(G109:G113)</f>
@@ -34715,7 +34718,7 @@
     </row>
     <row r="115" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="353" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B115" s="353"/>
       <c r="C115" s="353"/>
@@ -34731,7 +34734,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="354" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B117" s="354"/>
       <c r="C117" s="354"/>
@@ -34761,7 +34764,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="348" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B119" s="287" t="n">
         <f aca="false">B22*12%*B24*B25</f>
@@ -34786,7 +34789,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="348" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B120" s="287" t="n">
         <f aca="false">B16+B119+B29</f>
@@ -34811,7 +34814,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="348" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B121" s="292" t="n">
         <f aca="false">IFERROR(B10/B120,0)</f>
@@ -34836,7 +34839,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="348" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B122" s="287" t="str">
         <f aca="false">IF(B121&gt;=12%,"متوافق","فجوة")</f>
@@ -34861,7 +34864,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="348" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B123" s="287" t="n">
         <f aca="false">B22*15%*B24*B25</f>
@@ -34886,7 +34889,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="348" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B124" s="287" t="n">
         <f aca="false">B16+B123+B29</f>
@@ -34911,7 +34914,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="348" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B125" s="292" t="n">
         <f aca="false">IFERROR(B10/B124,0)</f>
@@ -34936,7 +34939,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="348" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B126" s="287" t="str">
         <f aca="false">IF(B125&gt;=12%,"متوافق","فجوة")</f>
@@ -34961,7 +34964,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="348" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B127" s="287" t="n">
         <f aca="false">B22*18%*B24*B25</f>
@@ -34986,7 +34989,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="348" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B128" s="287" t="n">
         <f aca="false">B16+B127+B29</f>
@@ -35011,7 +35014,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="348" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B129" s="292" t="n">
         <f aca="false">IFERROR(B10/B128,0)</f>
@@ -35036,7 +35039,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="348" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B130" s="287" t="str">
         <f aca="false">IF(B129&gt;=12%,"متوافق","فجوة")</f>
@@ -35061,7 +35064,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="353" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B131" s="353"/>
       <c r="C131" s="353"/>
@@ -35115,7 +35118,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="355" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B1" s="355"/>
       <c r="C1" s="355"/>
@@ -35127,7 +35130,7 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="356" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B2" s="356"/>
       <c r="C2" s="356"/>
@@ -35152,415 +35155,415 @@
         <v>83</v>
       </c>
       <c r="B4" s="357" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C4" s="357" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="D4" s="357" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E4" s="357" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F4" s="357" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="G4" s="357" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H4" s="357" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="358" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B5" s="358" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C5" s="359" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="D5" s="358" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="E5" s="359" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="F5" s="359" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="G5" s="358" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H5" s="358" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="358" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B6" s="358" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C6" s="359" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D6" s="358" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E6" s="359" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="F6" s="359" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="G6" s="358" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H6" s="358" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="358" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B7" s="358" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C7" s="359" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="D7" s="358" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="E7" s="359" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="F7" s="359" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="G7" s="358" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H7" s="358" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="358" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B8" s="358" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C8" s="359" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="D8" s="358" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="E8" s="359" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F8" s="359" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="G8" s="358" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H8" s="358" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="358" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B9" s="358" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="C9" s="359" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D9" s="358" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="E9" s="359" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F9" s="359" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="G9" s="358" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H9" s="358" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="358" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B10" s="358" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C10" s="359" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="D10" s="358" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E10" s="359" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="F10" s="359" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="G10" s="358" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H10" s="358" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="358" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B11" s="358" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="C11" s="359" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D11" s="358" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="E11" s="359" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="F11" s="359" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="G11" s="358" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H11" s="358" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="358" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B12" s="358" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C12" s="359" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="D12" s="358" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="E12" s="359" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F12" s="359" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="G12" s="358" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H12" s="358" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="358" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B13" s="358" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C13" s="359" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D13" s="358" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E13" s="359" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F13" s="359" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G13" s="358" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H13" s="358" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="358" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B14" s="358" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C14" s="359" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D14" s="358" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="E14" s="359" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F14" s="359" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="G14" s="358" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H14" s="358" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="358" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B15" s="358" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="C15" s="359" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="D15" s="358" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="E15" s="359" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F15" s="359" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="G15" s="358" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H15" s="358" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="358" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B16" s="358" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C16" s="359" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D16" s="358" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="E16" s="359" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="F16" s="359" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="G16" s="358" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H16" s="358" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="342" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B17" s="342" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C17" s="342" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D17" s="342" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="E17" s="342" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="F17" s="342" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="G17" s="342" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H17" s="342" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="342" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B18" s="342" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C18" s="342" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D18" s="342" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="E18" s="342" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="F18" s="342" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="G18" s="342" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H18" s="342" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="342" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B19" s="342" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C19" s="342" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="D19" s="342" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="E19" s="342" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="F19" s="342" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="G19" s="342" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H19" s="342" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
   </sheetData>
@@ -35592,7 +35595,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="360" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B1" s="360"/>
       <c r="C1" s="360"/>
@@ -35630,7 +35633,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="304" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B4" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!B13</f>
@@ -35638,7 +35641,7 @@
       </c>
       <c r="C4" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!C13</f>
-        <v>5.05426192003465</v>
+        <v>4.86287064177048</v>
       </c>
       <c r="D4" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!D13</f>
@@ -35655,7 +35658,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="304" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B5" s="301" t="n">
         <f aca="false">'Regulatory Capital Plan'!B14</f>
@@ -35680,7 +35683,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="304" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B6" s="286" t="str">
         <f aca="false">'Regulatory Capital Plan'!B16</f>
@@ -35705,51 +35708,51 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="304" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B7" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!B12-'Regulatory Capital Plan'!B14*'Regulatory Capital Plan'!B10)</f>
+        <f aca="false">'Regulatory Capital Plan'!B76</f>
         <v>0</v>
       </c>
       <c r="C7" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!C12-'Regulatory Capital Plan'!C14*'Regulatory Capital Plan'!C10)</f>
-        <v>77177818.7566001</v>
+        <f aca="false">'Regulatory Capital Plan'!C76</f>
+        <v>65653018.7566001</v>
       </c>
       <c r="D7" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!D12-'Regulatory Capital Plan'!D14*'Regulatory Capital Plan'!D10)</f>
+        <f aca="false">'Regulatory Capital Plan'!D76</f>
         <v>0</v>
       </c>
       <c r="E7" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!E12-'Regulatory Capital Plan'!E14*'Regulatory Capital Plan'!E10)</f>
+        <f aca="false">'Regulatory Capital Plan'!E76</f>
         <v>0</v>
       </c>
       <c r="F7" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!F12-'Regulatory Capital Plan'!F14*'Regulatory Capital Plan'!F10)</f>
+        <f aca="false">'Regulatory Capital Plan'!F76</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="304" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B8" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!B12/'Regulatory Capital Plan'!B14-'Regulatory Capital Plan'!B10)</f>
+        <f aca="false">'Regulatory Capital Plan'!B77</f>
         <v>0</v>
       </c>
       <c r="C8" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!C12/'Regulatory Capital Plan'!C14-'Regulatory Capital Plan'!C10)</f>
-        <v>19294454.68915</v>
+        <f aca="false">'Regulatory Capital Plan'!C77</f>
+        <v>16413254.68915</v>
       </c>
       <c r="D8" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!D12/'Regulatory Capital Plan'!D14-'Regulatory Capital Plan'!D10)</f>
+        <f aca="false">'Regulatory Capital Plan'!D77</f>
         <v>0</v>
       </c>
       <c r="E8" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!E12/'Regulatory Capital Plan'!E14-'Regulatory Capital Plan'!E10)</f>
+        <f aca="false">'Regulatory Capital Plan'!E77</f>
         <v>0</v>
       </c>
       <c r="F8" s="363" t="n">
-        <f aca="false">MAX(0,'Regulatory Capital Plan'!F12/'Regulatory Capital Plan'!F14-'Regulatory Capital Plan'!F10)</f>
+        <f aca="false">'Regulatory Capital Plan'!F77</f>
         <v>0</v>
       </c>
     </row>
@@ -35780,7 +35783,7 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="304" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B10" s="292" t="n">
         <f aca="false">'Funding &amp; Liquidity'!B21</f>
@@ -35830,7 +35833,7 @@
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="304" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B12" s="293" t="n">
         <f aca="false">'Basel III'!B96</f>
@@ -35863,7 +35866,7 @@
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="364" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B14" s="364"/>
       <c r="C14" s="364"/>
@@ -35873,7 +35876,7 @@
     </row>
     <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="365" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B15" s="365"/>
       <c r="C15" s="365"/>
@@ -35891,7 +35894,7 @@
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="364" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B17" s="364"/>
       <c r="C17" s="364"/>
@@ -35901,24 +35904,24 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="321" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B18" s="321" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="C18" s="321"/>
       <c r="D18" s="366" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="E18" s="366"/>
       <c r="F18" s="366"/>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="321" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B19" s="321" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C19" s="321"/>
       <c r="D19" s="366" t="s">
@@ -35929,24 +35932,24 @@
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="321" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B20" s="321" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C20" s="321"/>
       <c r="D20" s="366" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="E20" s="366"/>
       <c r="F20" s="366"/>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="321" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B21" s="321" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C21" s="321"/>
       <c r="D21" s="361"/>
@@ -35955,10 +35958,10 @@
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="321" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B22" s="321" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C22" s="321"/>
       <c r="D22" s="361"/>
@@ -35967,10 +35970,10 @@
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="321" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B23" s="321" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="C23" s="321"/>
       <c r="D23" s="361"/>
@@ -35979,10 +35982,10 @@
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="321" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B24" s="321" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C24" s="321"/>
       <c r="D24" s="361"/>
@@ -35991,7 +35994,7 @@
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="364" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B26" s="364"/>
       <c r="C26" s="364"/>
@@ -36001,7 +36004,7 @@
     </row>
     <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="365" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B27" s="365"/>
       <c r="C27" s="365"/>
@@ -36011,7 +36014,7 @@
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="364" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B29" s="364"/>
       <c r="C29" s="364"/>
@@ -36021,14 +36024,14 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="362" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B30" s="362" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C30" s="362"/>
       <c r="D30" s="362" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E30" s="362"/>
       <c r="F30" s="362"/>
@@ -36038,11 +36041,11 @@
         <v>1</v>
       </c>
       <c r="B31" s="321" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C31" s="321"/>
       <c r="D31" s="367" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="E31" s="367"/>
       <c r="F31" s="367"/>
@@ -36052,11 +36055,11 @@
         <v>2</v>
       </c>
       <c r="B32" s="321" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="C32" s="321"/>
       <c r="D32" s="367" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="E32" s="367"/>
       <c r="F32" s="367"/>
@@ -36066,11 +36069,11 @@
         <v>3</v>
       </c>
       <c r="B33" s="321" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="C33" s="321"/>
       <c r="D33" s="367" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="E33" s="367"/>
       <c r="F33" s="367"/>
@@ -36080,11 +36083,11 @@
         <v>4</v>
       </c>
       <c r="B34" s="321" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="C34" s="321"/>
       <c r="D34" s="367" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="E34" s="367"/>
       <c r="F34" s="367"/>
@@ -36094,11 +36097,11 @@
         <v>5</v>
       </c>
       <c r="B35" s="321" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="C35" s="321"/>
       <c r="D35" s="367" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="E35" s="367"/>
       <c r="F35" s="367"/>
@@ -36108,11 +36111,11 @@
         <v>6</v>
       </c>
       <c r="B36" s="321" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C36" s="321"/>
       <c r="D36" s="367" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="E36" s="367"/>
       <c r="F36" s="367"/>
@@ -36122,11 +36125,11 @@
         <v>7</v>
       </c>
       <c r="B37" s="321" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C37" s="321"/>
       <c r="D37" s="367" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="E37" s="367"/>
       <c r="F37" s="367"/>
@@ -36136,11 +36139,11 @@
         <v>8</v>
       </c>
       <c r="B38" s="321" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C38" s="321"/>
       <c r="D38" s="367" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="E38" s="367"/>
       <c r="F38" s="367"/>
@@ -36150,11 +36153,11 @@
         <v>9</v>
       </c>
       <c r="B39" s="321" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C39" s="321"/>
       <c r="D39" s="367" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="E39" s="367"/>
       <c r="F39" s="367"/>
@@ -36164,11 +36167,11 @@
         <v>10</v>
       </c>
       <c r="B40" s="113" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C40" s="113"/>
       <c r="D40" s="368" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="E40" s="113"/>
       <c r="F40" s="113"/>
@@ -36178,18 +36181,18 @@
         <v>11</v>
       </c>
       <c r="B41" s="365" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="C41" s="365"/>
       <c r="D41" s="365" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="E41" s="365"/>
       <c r="F41" s="365"/>
     </row>
     <row r="42" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="370" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B42" s="370"/>
       <c r="C42" s="370"/>

--- a/deliverables/flexy-fra-financial-model/Flexy_FRA_Financial_Model_Year1_Year5_FINAL.xlsx
+++ b/deliverables/flexy-fra-financial-model/Flexy_FRA_Financial_Model_Year1_Year5_FINAL.xlsx
@@ -3435,7 +3435,7 @@
     <t xml:space="preserve">تفعيل سيناريو تأخر الترخيص النهائي (المادتان 3/4 و4 من قرار 268/2023 - مدة أقصاها سنتان من تاريخ الترخيص المبدئي)</t>
   </si>
   <si>
-    <t xml:space="preserve">خلية زرقاء: 1 = مفعل (سقف 4× يمتد إلى بداية Year 3)، 0 = غير مفعل (سقف 9× يبدأ خلال Year 2 وفق الموعد التخطيطي)</t>
+    <t xml:space="preserve">خلية زرقاء - مرجعية فقط: سقف 4x من صافي حقوق الملكية يسري إلزاميا طوال Year 1 وYear 2 بالكامل بصرف النظر عن هذا التفعيل؛ 9x من القاعدة الرأسمالية التنظيمية لا يبدأ إلا من Year 3 وبافتراض صدور الترخيص النهائي فعليا.</t>
   </si>
   <si>
     <t xml:space="preserve">أرصدة Year 2 كما في الخطة الأصلية</t>
@@ -3447,7 +3447,7 @@
     <t xml:space="preserve">السيناريو لا يغير رصيد الدين، فقط القاعدة الرأسمالية</t>
   </si>
   <si>
-    <t xml:space="preserve">قاعدة القياس قبل الضخ (9×: القاعدة الرأسمالية؛ 4× عند التأخير: صافي حقوق الملكية)</t>
+    <t xml:space="preserve">قاعدة القياس قبل الضخ: صافي حقوق الملكية (السقف الساري طوال Year 1 وYear 2 هو 4× دائما وفق قرار 268/2023)</t>
   </si>
   <si>
     <t xml:space="preserve">قرار 268/2023 يستخدم صافي حقوق الملكية أثناء مرحلة 4×؛ خصومات CAR تخص حساب كفاية رأس المال</t>
@@ -3459,13 +3459,13 @@
     <t xml:space="preserve">السقف الواجب التطبيق</t>
   </si>
   <si>
-    <t xml:space="preserve">العمود الأيسر: افتراض ترخيص نهائي خلال Year 2 وفق الموعد المستهدف</t>
+    <t xml:space="preserve">العمود الأيسر = الحالة الأساسية المعتمدة دون ضخ إضافي؛ العمود الأيمن = سيناريو الضخ لإغلاق الفجوة. السقف الساري لكلا العمودين طوال Year 1 وYear 2 هو 4x صافي حقوق الملكية؛ 9x القاعدة الرأسمالية التنظيمية يبدأ من Year 3 فقط بافتراض الترخيص النهائي الفعلي.</t>
   </si>
   <si>
     <t xml:space="preserve">الرافعة المالية قبل الضخ</t>
   </si>
   <si>
-    <t xml:space="preserve">يختلف مقام القياس حسب المرحلة: 9× يستخدم القاعدة الرأسمالية التخطيطية، و4× يستخدم صافي حقوق الملكية وفق قرار 268/2023</t>
+    <t xml:space="preserve">4x صافي حقوق الملكية يسري طوال Year 1 وYear 2 وفق قرار 268/2023؛ 9x القاعدة الرأسمالية التنظيمية يبدأ من Year 3 فقط بافتراض صدور الترخيص النهائي فعليا - لا ينطبق على Year 2 في أي حال.</t>
   </si>
   <si>
     <t xml:space="preserve">حالة الرافعة قبل الضخ</t>
@@ -29183,11 +29183,11 @@
         <v>1131</v>
       </c>
       <c r="B8" s="287" t="n">
-        <f aca="false">'Regulatory Capital Plan'!C10</f>
-        <v>73205545.31085</v>
+        <f aca="false">'Regulatory Capital Plan'!C7</f>
+        <v>76086745.31085</v>
       </c>
       <c r="C8" s="287" t="n">
-        <f aca="false">IF(C4=1,'Regulatory Capital Plan'!C7,'Regulatory Capital Plan'!C10)</f>
+        <f aca="false">'Regulatory Capital Plan'!C7</f>
         <v>76086745.31085</v>
       </c>
       <c r="D8" s="286" t="s">
@@ -29211,7 +29211,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="301" t="n">
-        <f aca="false">IF(C4=1,4,9)</f>
+        <f aca="false">'Regulatory Capital Plan'!C14</f>
         <v>4</v>
       </c>
       <c r="D11" s="286" t="s">
@@ -29224,7 +29224,7 @@
       </c>
       <c r="B12" s="301" t="n">
         <f aca="false">B7/B8</f>
-        <v>5.05426192003465</v>
+        <v>4.86287064177048</v>
       </c>
       <c r="C12" s="301" t="n">
         <f aca="false">B7/C8</f>
@@ -29278,7 +29278,7 @@
       </c>
       <c r="B17" s="287" t="n">
         <f aca="false">MAX(0,B16-B8)</f>
-        <v>19294454.68915</v>
+        <v>16413254.68915</v>
       </c>
       <c r="C17" s="287" t="n">
         <f aca="false">MAX(0,C16-C8)</f>
@@ -29292,7 +29292,7 @@
       </c>
       <c r="B18" s="287" t="n">
         <f aca="false">B17</f>
-        <v>19294454.68915</v>
+        <v>16413254.68915</v>
       </c>
       <c r="C18" s="287" t="n">
         <f aca="false">C17</f>
@@ -29319,7 +29319,10 @@
       <c r="A20" s="113" t="s">
         <v>1146</v>
       </c>
-      <c r="B20" s="113"/>
+      <c r="B20" s="113" t="n">
+        <f aca="false">MAX(0,B7-B11*B8)</f>
+        <v>65653018.7566001</v>
+      </c>
       <c r="C20" s="113" t="n">
         <f aca="false">MAX(0,C7-C11*C8)</f>
         <v>65653018.7566001</v>
@@ -29342,7 +29345,7 @@
       </c>
       <c r="B22" s="287" t="n">
         <f aca="false">B8+B19</f>
-        <v>73205545.31085</v>
+        <v>76086745.31085</v>
       </c>
       <c r="C22" s="287" t="n">
         <f aca="false">C8+C19</f>
@@ -29356,7 +29359,7 @@
       </c>
       <c r="B23" s="301" t="n">
         <f aca="false">B7/B22</f>
-        <v>5.05426192003465</v>
+        <v>4.86287064177048</v>
       </c>
       <c r="C23" s="301" t="n">
         <f aca="false">B7/C22</f>
